--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0017.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0017.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Hồi Concerto Energy từ Floral Ravage</t>
+          <t>Hồi Phục Bản Giao Hưởng Flora Tàn Phá</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>DMG Ephemeral</t>
+          <t>Sát Thương Phù Du</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Thời gian Budding Mode</t>
+          <t>Thời gian Chế Độ Nảy Mầm</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Cooldown Phù Du</t>
+          <t>Hồi Chiêu Phù Du</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Heavy Attack: Kích Nổ: Giữ {0} và thả khi con trỏ nằm trong vùng Băng Giá</t>
+          <t>Đòn Heavy Attack: Kích Nổ: Giữ {0} và thả khi con trỏ nằm trong vùng Băng Giá</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Ice Burst: Dùng Đòn tấn công mạnh: Detonate để xuyên thủng Ice Thorn, Ice Prism hoặc Glacier</t>
+          <t>Vụ nổ băng: Dùng Đòn tấn công mạnh: Kích nổ để xuyên thủng Ice Thorn, Ice Prism hoặc Glacier</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Heavy Attack: Giữ rồi thả {0}</t>
+          <t>Đòn Heavy Attack: Giữ rồi thả {0}</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Sử dụng Heavy Attack để tiêu hao Thanh Forte: Khi Thanh Forte không trống, giữ {0}.</t>
+          <t>Sử dụng Đòn Tấn Công Mạnh để tiêu hao Thanh Forte: Khi Thanh Forte không trống, giữ {0}.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Striding Lion: Khi Thanh Forte đầy, giữ {0}</t>
+          <t>Sư Tử Bước Đi: Khi Thanh Forte đầy, giữ {0}</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Striding Lion: Sau khi sử dụng Intro Skill hoặc Resonance Liberation, nhấn {0} nếu Thanh Forte đã đầy</t>
+          <t>Sư Tử Bước Đi: Sau khi sử dụng Kỹ Năng Khởi Động hoặc Resonance Liberation, nhấn {0} nếu Thanh Forte đã đầy</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Cloudy Cuồng Loạn: Khi Thanh Forte đạt 100, giữ {0}</t>
+          <t>U Ám Cuồng Loạn: Khi Thanh Forte đạt 100, giữ {0}</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Vỡ Cosmos: Trong trạng thái Resonance Liberation, giữ {0} khi Thanh Forte đạt 100</t>
+          <t>Vỡ Vũ Trụ: Trong trạng thái Resonance Liberation, giữ {0} khi Thanh Forte đạt 100</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>"Mercy": Khi Thanh Forte đạt 3, giữ {0}</t>
+          <t>"Lòng thương xót": Khi Thanh Forte đạt 3, giữ {0}</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>""Messenger Tử Thần": Trong trạng thái Resonance Liberation, nhấn {0} khi Thanh Forte đạt 5"</t>
+          <t>""Sứ Giả Tử Thần": Trong trạng thái Resonance Liberation, nhấn {0} khi Thanh Forte đạt 5"</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press}&lt;/color&gt; {0} ngay sau khi sử dụng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để thực hiện Stage 4 Basic Attack và nhận được Trigram - Lôi.</t>
+          <t>&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press}&lt;/color&gt; {0} ngay sau khi sử dụng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để thực hiện Giai Đoạn 4 Đòn Basic Attack và nhận được Quẻ - Lôi.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Decipher: Khi Thanh Forte đầy, nhấn {1}+{0}.</t>
+          <t>Giải mã: Khi Thanh Forte đầy, nhấn {1}+{0}.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Feather Fall: Khi Thanh Forte đạt 3, nhấn {0} khi đang ở giữa không trung</t>
+          <t>Rơi Nhẹ Nhàng: Khi Thanh Forte đạt 3, nhấn {0} khi đang ở giữa không trung</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Heavy Attack: Song Gió: Trong khi thực hiện Heavy Attack, nhấn {0}</t>
+          <t>Đòn Heavy Attack: Khúc Ca Gió: Trong khi thực hiện Đòn Heavy Attack, nhấn {0}</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Emerald Storm: Kết Cục: Khi Thanh Forte trên 30, nhấn {0}</t>
+          <t>Bão Ngọc Lục Bảo: Kết Cục: Khi Thanh Forte trên 30, nhấn {0}</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Heavy Attack: Giữ {0}</t>
+          <t>Đòn Heavy Attack: Giữ {0}</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Đòn Attack Gió Bay: Trong khi tấn công mạnh, giữ {0}</t>
+          <t>Đòn Tấn Công Gió Bay: Trong khi tấn công mạnh, giữ {0}</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Chém Abyssal: Trong Heavy Attack, giải phóng {0}</t>
+          <t>Chém Vực Sâu: Trong Đòn Tấn Công Mạnh, giải phóng {0}</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Emerald Storm: Khúc Dạo Đầu: Khi Thanh Forte dưới 30, nhấn {0}</t>
+          <t>Bão Ngọc Lục Bảo: Khúc Dạo Đầu: Khi Thanh Forte dưới 30, nhấn {0}</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Sử dụng &lt;color=Highlight&gt;Blessed Giọng nói&lt;/color&gt; để biểu diễn &lt;color=Highlight&gt;Solo Concert&lt;/color&gt;: {0}+{0}+{0}+{0} hoặc Kỹ Năng Mở Đầu+{0}+{0}</t>
+          <t>Sử dụng &lt;color=Highlight&gt;Giọng Hát Phúc Lành&lt;/color&gt; để biểu diễn &lt;color=Highlight&gt;Độc Tấu&lt;/color&gt;: {0}+{0}+{0}+{0} hoặc Kỹ Năng Mở Đầu+{0}+{0}</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Sử dụng &lt;color=Highlight&gt;Vibrating Strings&lt;/color&gt; để biểu diễn &lt;color=Highlight&gt;Solo Concert&lt;/color&gt;: {1}+{0}+{0}+{0} hoặc Dodge Counter+{0}+{0}.</t>
+          <t>Sử dụng &lt;color=Highlight&gt;Dây Đàn Rung Động&lt;/color&gt; để biểu diễn &lt;color=Highlight&gt;Độc Tấu Hoàn Mỹ&lt;/color&gt;: {1}+{0}+{0}+{0} hoặc Dodge Counter Tránh+{0}+{0}.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Fleurdelys&lt;/color&gt; Stage 2 Resonance Skill: {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} sau khi sử dụng Stage 1 Resonance Skill &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Fleurdelys&lt;/color&gt; Giai Đoạn 2 Resonance Skill: {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} sau khi sử dụng Giai Đoạn 1 Resonance Skill &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Fleurdelys&lt;/color&gt; Stage 2 Heavy Attack Cường Hóa: Giữ {0} rồi {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} lần nữa.</t>
+          <t>&lt;color=Highlight&gt;Fleurdelys&lt;/color&gt; Giai Đoạn 2 Đòn Heavy Attack Cường Hóa: Giữ {0} rồi {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} lần nữa.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Resonance Liberation - Blade of Howling Squall&lt;/color&gt;: Khi ở dạng &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} khi &lt;color=Highlight&gt;Conviction&lt;/color&gt; đạt 120 điểm.</t>
+          <t>&lt;color=Highlight&gt;Resonance Liberation - Lưỡi Kiếm Gió Gào&lt;/color&gt;: Khi ở dạng &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} khi &lt;color=Highlight&gt;Niềm Tin&lt;/color&gt; đạt 120 điểm.</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Lunar Cycle&lt;/color&gt;: {Cus:Ipt,Touch=Touch PC=press Gamepad=press} {1} sau khi tung chiêu Basic Attack Cấp 3, Intro Skill hoặc Resonance Skill - Pulse of Origins.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Lunar Cycle&lt;/color&gt;: {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {1} sau khi tung chiêu Basic Attack Cấp 3, Kỹ Năng Khởi Động hoặc Resonance Skill - Pulse of Origins.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Summon lãnh địa &lt;color=Highlight&gt;Full Moon&lt;/color&gt;: Khi Concerto Energy đầy, giữ {0}.</t>
+          <t>Triệu hồi lãnh địa &lt;color=Highlight&gt;Trăng Tròn&lt;/color&gt;: Khi Concerto Energy đầy, giữ {0}.</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Heavy Attack - Resonance: Sau Basic Attack Stage 3 hoặc Heavy Attack, {0} đúng lúc</t>
+          <t>Heavy Attack - Cộng Hưởng: Sau Basic Attack Giai Đoạn 3 hoặc Heavy Attack, {0} đúng lúc</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Heavy Attack: Aftertune: Nhấn {0} sau khi Heavy Attack: Resonance trúng mục tiêu</t>
+          <t>Đòn Heavy Attack: Aftertune: Tap {0} after Heavy Attack: Resonance hits a target</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Heavy Attack: Starflower Nở: Khi Thanh Forte chưa cạn, giữ {0}</t>
+          <t>Đòn Heavy Attack: Hoa Sao Nở: Khi Thanh Forte chưa cạn, giữ {0}</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Mid-air Attack: Starflower Nở – Khi Thanh Forte chưa cạn, nhấn {0} giữa không trung</t>
+          <t>Mid-air Attack: Hoa Sao Nở – Khi Thanh Forte chưa cạn, nhấn {0} giữa không trung</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Phán Đoán: Khi Siêu Cấp Tinh Vực tồn tại, Shorekeeper có thể sử dụng Intro Skill Phán Đoán.</t>
+          <t>Phán Đoán: Khi Siêu Cấp Tinh Vực tồn tại, Shorekeeper có thể sử dụng Kỹ Năng Khởi Động Phán Đoán.</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Butterfly Nhị Phân: Khi Outro Skill của Shorekeeper có hiệu lực, nhấn {0} sẽ giúp Resonator hiện tại hồi phục khỏi gián đoạn khi bị đánh trúng hoặc tung lên, được tính là Dodge thành công. Hiệu ứng này chỉ kích hoạt được số lần giới hạn.</t>
+          <t>Bướm Nhị Phân: Khi Kỹ Năng Outro của Shorekeeper có hiệu lực, nhấn {0} sẽ giúp Resonator hiện tại hồi phục khỏi gián đoạn khi bị đánh trúng hoặc tung lên, được tính là né thành công. Hiệu ứng này chỉ kích hoạt được số lần giới hạn.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Heavy Attack - Sao Lóe: Khi Phoebe ở trạng thái Absolution hoặc Confession, giữ {0} sau khi thực hiện Basic Attack 3 để tấn công mục tiêu, tiêu hao Divine Giọng nói. Ở trạng thái Absolution, Phoebe gây sát thương cao hơn và tiêu hao ít Divine Giọng nói hơn. Ở trạng thái Confession, Phoebe áp dụng Spectro Frazzle lên mục tiêu trúng đòn.</t>
+          <t>Tấn Công Mạnh - Sao Lóe: Khi Phoebe ở trạng thái Absolution hoặc Confession, giữ {0} sau khi thực hiện Basic Attack 3 để tấn công mục tiêu, tiêu hao Divine Voice. Ở trạng thái Absolution, Phoebe gây sát thương cao hơn và tiêu hao ít Divine Voice hơn. Ở trạng thái Confession, Phoebe áp dụng Spectro Frazzle lên mục tiêu trúng đòn.</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} Resonance Skill để triệu hồi Vòng Gương, hút mục tiêu vào và làm chúng trì trệ. {Cus:Ipt,Touch=Touch PC=press Gamepad=press} {0} trong thời gian giới hạn để dịch chuyển đến Vòng Gương. Phoebe có bộ kỹ năng Basic Attack khác nhau khi ở trong và ngoài Vòng Gương.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Resonance Skill để triệu hồi Vòng Gương, hút mục tiêu vào và làm chúng trì trệ. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} trong thời gian giới hạn để dịch chuyển đến Vòng Gương. Phoebe có bộ kỹ năng Basic Attack khác nhau khi ở trong và ngoài Vòng Gương.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Resonance Liberation - Tư Thế Cuối Cùng: Ở Chế Độ Hỏa Diệm, {Cus:Ipt,Touch=tấn PC=press Gamepad=press} {2} khi Blaze dưới 30 hoặc sau 8 giây kể từ khi vào Chế Độ Hỏa Diệm.</t>
+          <t>Resonance Liberation - Tư Thế Cuối Cùng: Ở Chế Độ Hỏa Diệm, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {2} khi Blaze dưới 30 hoặc sau 8 giây kể từ khi vào Chế Độ Hỏa Diệm.</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Trong trạng thái &lt;color=Highlight&gt;Optical Sampling Stage&lt;/color&gt;, Normal Attack, Resonance Skill, Lynae-Style Palettes và Dodge Counter sẽ hồi phục &lt;color=Highlight&gt;Overflow&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Giai Đoạn Lấy Mẫu Quang Học&lt;/color&gt;, Normal Attack, Resonance Skill, Bảng Màu Kiểu Lynae và Dodge Counter Tránh sẽ hồi phục &lt;color=Highlight&gt;Tràn Dòng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt; và trượt trên mặt đất, &lt;color=Highlight&gt;Lumiflow&lt;/color&gt; sẽ liên tục hồi phục. Sử dụng &lt;color=Highlight&gt;Polychrome Leap&lt;/color&gt; sẽ tiêu hao &lt;color=Highlight&gt;Lumiflow&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;True Color&lt;/color&gt;.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Diễu Hành Muôn Màu&lt;/color&gt; và trượt trên mặt đất, &lt;color=Highlight&gt;Dòng Sáng&lt;/color&gt; sẽ liên tục hồi phục. Sử dụng &lt;color=Highlight&gt;Nhảy Đa Sắc&lt;/color&gt; sẽ tiêu hao &lt;color=Highlight&gt;Dòng Sáng&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Sắc Thật&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Kính Hồng Ruby: Dodge Counter + {1} + {1}</t>
+          <t>Kính Hồng Ruby: Né Phản Đòn + {1} + {1}</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Basic Attack Chain: Sau khi thực hiện Basic Attack 3, giữ {0} để liên tục tấn công mục tiêu.</t>
+          <t>Basic Attack Dây Xích: Sau khi thực hiện Basic Attack 3, giữ {0} để liên tục tấn công mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Chain Attack - Điệu Valse Uốn Lượn: Khi thực hiện Basic Attack 3, giữ {0} để liên tục tấn công mục tiêu.</t>
+          <t>Tấn Công Dây Xích - Điệu Valse Uốn Lượn: Khi thực hiện Basic Attack 3, giữ {0} để liên tục tấn công mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để kéo các mục tiêu gần lại và tung Roccia lên không trung, kích hoạt Beyond Imagination.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} để kéo các mục tiêu gần lại và tung Roccia lên không trung, kích hoạt Beyond Imagination.</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Attack Nâng Cao - Hecate: Khi ở trạng thái Maestro, {0}+{0}+{0}, hoặc kích hoạt khi Resonators khác trong đội sử dụng Kỹ Năng Echo.</t>
+          <t>Tấn Công Nâng Cao - Hecate: Khi ở trạng thái Maestro, {0}+{0}+{0}, hoặc kích hoạt khi Resonator khác trong đội sử dụng Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Hiệu ứng Glacio Chafe</t>
+          <t>Hiệu Ứng Xước Băng Giá</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Effect Bùng Nổ Fusion</t>
+          <t>Hiệu Ứng Bùng Nổ Hợp Nhất</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Hiệu ứng Spectro Frazzle</t>
+          <t>Hiệu Ứng Rối Loạn Spectro</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Hiệu ứng Havoc Bane</t>
+          <t>Hiệu Ứng Hiểm Họa Havoc</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Khuếch đại Glacio DMG</t>
+          <t>Khuếch Đại Sát Thương Băng giá</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Khuếch đại Fusion DMG</t>
+          <t>Khuếch Đại Sát Thương Hợp Thể</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Khuếch đại Aero DMG</t>
+          <t>Khuếch Đại Sát Thương Aero</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Khuếch đại Electro DMG</t>
+          <t>Khuếch Đại Sát Thương Electro</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Khuếch đại Electro DMG</t>
+          <t>Khuếch Đại Sát Thương Electro</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Khuếch đại Havoc DMG</t>
+          <t>Khuếch Đại Sát Thương Havoc</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Glacio DMG</t>
+          <t>Sát Thương Glacio</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Fusion DMG</t>
+          <t>Sát Thương Fusion</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Electro DMG</t>
+          <t>Sát Thương Electro</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Spectro DMG</t>
+          <t>Sát Thương Spectro</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Havoc DMG</t>
+          <t>Sát Thương Havoc</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>DMG Amplification Kiếm</t>
+          <t>Khuếch Đại Sát Thương Kiếm</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>DMG Amplification Broadblade</t>
+          <t>Khuếch Đại Sát Thương Kiếm Rộng</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Tăng DMG Súng ngắn</t>
+          <t>Khuếch Đại Sát Thương Súng Lục</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Khuếch đại sát thương Rectifier</t>
+          <t>Khuếch đại DMG Bộ điều chỉnh</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Tăng DMG Quả đấm</t>
+          <t>Khuếch Đại Sát Thương Bao Tay</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>DMG Amplification Resonance Skill</t>
+          <t>Khuếch Đại Sát Thương Resonance Skill</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Khuếch đại Sát thương Basic Attack</t>
+          <t>Khuếch đại DMG Basic Attack</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>DMG Amplification Resonance Liberation</t>
+          <t>Khuếch Đại Sát Thương Resonance Liberation</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>DMG Amplification Heavy Attack</t>
+          <t>Khuếch Đại Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Tăng DMG giữa không trung</t>
+          <t>Khuếch Đại Sát Thương Trên Không</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Khuếch đại DMG</t>
+          <t>Khuếch Đại Sát Thương</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Recovery STA</t>
+          <t>Hồi phục STA</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Effect Erosion Gió</t>
+          <t>Hiệu Ứng Aero Erosion</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Crit. DMG tăng {0}.</t>
+          <t>Crit. DMG tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Crit. DMG tăng {0}.</t>
+          <t>Crit. DMG tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Crit. DMG tăng {0}.</t>
+          <t>Crit. DMG tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Crit. DMG tăng {0}.</t>
+          <t>Crit. DMG tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Tỉ lệ Crit. tăng {0}.</t>
+          <t>Crit. Rate tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Tỉ lệ Crit. tăng {0}.</t>
+          <t>Crit. Rate tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Tỉ lệ Crit. tăng {0}.</t>
+          <t>Crit. Rate tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Tỉ lệ Crit. tăng {0}.</t>
+          <t>Crit. Rate tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus tăng thêm {0}.</t>
+          <t>Thêm Sát Thương Băng giá tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus+</t>
+          <t>Thêm Sát Thương Băng giá+</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Electro DMG Bonus tăng thêm {0}.</t>
+          <t>Thêm Sát Thương Electro tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Tăng Electro DMG Bonus</t>
+          <t>Thêm Sát Thương Electro+</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>DEF tăng {0}.</t>
+          <t>Phòng Ngự tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>DEF tăng {0}.</t>
+          <t>Phòng Ngự tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus tăng thêm {0}.</t>
+          <t>Thêm Sát Thương Băng giá tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus+</t>
+          <t>Thêm Sát Thương Băng giá+</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Electro DMG Bonus tăng thêm {0}.</t>
+          <t>Thêm Sát Thương Electro tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Tăng Electro DMG Bonus</t>
+          <t>Thêm Sát Thương Electro+</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Electro DMG Bonus tăng thêm {0}.</t>
+          <t>Thêm Sát Thương Electro tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Tăng Electro DMG Bonus</t>
+          <t>Thêm Sát Thương Electro+</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>DEF tăng {0}.</t>
+          <t>Phòng Ngự tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>DEF tăng {0}.</t>
+          <t>Phòng Ngự tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Electro DMG Bonus tăng thêm {0}.</t>
+          <t>Thêm Sát Thương Electro tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Tăng Electro DMG Bonus</t>
+          <t>Thêm Sát Thương Electro+</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus thêm {0}.</t>
+          <t>Tăng Sát Thương Aero thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus+</t>
+          <t>Tăng Sát Thương Aero+</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus thêm {0}.</t>
+          <t>Tăng Sát Thương Aero thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus+</t>
+          <t>Tăng Sát Thương Aero+</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus thêm {0}.</t>
+          <t>Tăng Sát Thương Aero thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus+</t>
+          <t>Tăng Sát Thương Aero+</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus thêm {0}.</t>
+          <t>Tăng Sát Thương Aero thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus+</t>
+          <t>Tăng Sát Thương Aero+</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus thêm {0}.</t>
+          <t>Tăng Sát Thương Aero thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus+</t>
+          <t>Tăng Sát Thương Aero+</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus tăng thêm {0}.</t>
+          <t>Thêm Sát Thương Băng giá tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus+</t>
+          <t>Thêm Sát Thương Băng giá+</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus thêm {0}.</t>
+          <t>Tăng Sát Thương Aero thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus+</t>
+          <t>Tăng Sát Thương Aero+</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus thêm {0}.</t>
+          <t>Tăng Sát Thương Aero thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus+</t>
+          <t>Tăng Sát Thương Aero+</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus thêm {0}.</t>
+          <t>Tăng Sát Thương Aero thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus+</t>
+          <t>Tăng Sát Thương Aero+</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Tỉ lệ Crit. tăng {0}.</t>
+          <t>Crit. Rate tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Tỉ lệ Crit. tăng {0}.</t>
+          <t>Crit. Rate tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Tỉ lệ Crit. tăng {0}.</t>
+          <t>Crit. Rate tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Tỉ lệ Crit. tăng {0}.</t>
+          <t>Crit. Rate tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Spectro DMG Bonus tăng {0}.</t>
+          <t>Thêm Sát Thương Spectro tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Tăng Spectro DMG Bonus</t>
+          <t>Thêm Sát Thương Spectro+</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Spectro DMG Bonus tăng {0}.</t>
+          <t>Thêm Sát Thương Spectro tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Tăng Spectro DMG Bonus</t>
+          <t>Thêm Sát Thương Spectro+</t>
         </is>
       </c>
     </row>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Spectro DMG Bonus tăng {0}.</t>
+          <t>Thêm Sát Thương Spectro tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Tăng Spectro DMG Bonus</t>
+          <t>Thêm Sát Thương Spectro+</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Spectro DMG Bonus tăng {0}.</t>
+          <t>Thêm Sát Thương Spectro tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Tăng Spectro DMG Bonus</t>
+          <t>Thêm Sát Thương Spectro+</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus lên thêm {0}.</t>
+          <t>Tăng Sát Thương Havoc lên thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus+</t>
+          <t>Tăng Sát Thương Havoc+</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>DEF tăng {0}.</t>
+          <t>Phòng Ngự tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>DEF tăng {0}.</t>
+          <t>Phòng Ngự tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus lên thêm {0}.</t>
+          <t>Tăng Sát Thương Havoc lên thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus+</t>
+          <t>Tăng Sát Thương Havoc+</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus lên thêm {0}.</t>
+          <t>Tăng Sát Thương Havoc lên thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus+</t>
+          <t>Tăng Sát Thương Havoc+</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>DEF tăng {0}.</t>
+          <t>Phòng Ngự tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>DEF tăng {0}.</t>
+          <t>Phòng Ngự tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus lên thêm {0}.</t>
+          <t>Tăng Sát Thương Havoc lên thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus+</t>
+          <t>Tăng Sát Thương Havoc+</t>
         </is>
       </c>
     </row>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus lên thêm {0}.</t>
+          <t>Tăng Sát Thương Havoc lên thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus+</t>
+          <t>Tăng Sát Thương Havoc+</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -17539,7 +17539,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus lên thêm {0}.</t>
+          <t>Tăng Sát Thương Havoc lên thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus+</t>
+          <t>Tăng Sát Thương Havoc+</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus lên thêm {0}.</t>
+          <t>Tăng Sát Thương Havoc lên thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus+</t>
+          <t>Tăng Sát Thương Havoc+</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -17929,7 +17929,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus lên thêm {0}.</t>
+          <t>Tăng Sát Thương Havoc lên thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus+</t>
+          <t>Tăng Sát Thương Havoc+</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Crit. DMG tăng {0}.</t>
+          <t>Crit. DMG tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -18319,7 +18319,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Crit. DMG tăng {0}.</t>
+          <t>Crit. DMG tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Crit. DMG tăng {0}.</t>
+          <t>Crit. DMG tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Crit. DMG tăng {0}.</t>
+          <t>Crit. DMG tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -19489,7 +19489,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus lên thêm {0}.</t>
+          <t>Tăng Sát Thương Havoc lên thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus+</t>
+          <t>Tăng Sát Thương Havoc+</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus lên thêm {0}.</t>
+          <t>Tăng Sát Thương Havoc lên thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus+</t>
+          <t>Tăng Sát Thương Havoc+</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus lên thêm {0}.</t>
+          <t>Tăng Sát Thương Havoc lên thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20074,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus+</t>
+          <t>Tăng Sát Thương Havoc+</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus lên thêm {0}.</t>
+          <t>Tăng Sát Thương Havoc lên thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -20464,7 +20464,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus+</t>
+          <t>Tăng Sát Thương Havoc+</t>
         </is>
       </c>
     </row>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Tỉ lệ Crit. tăng {0}.</t>
+          <t>Crit. Rate tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Tỉ lệ Crit. tăng {0}.</t>
+          <t>Crit. Rate tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Tỉ lệ Crit. tăng {0}.</t>
+          <t>Crit. Rate tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Tỉ lệ Crit. tăng {0}.</t>
+          <t>Crit. Rate tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Tỉ lệ Crit. tăng {0}.</t>
+          <t>Crit. Rate tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Tỉ lệ Crit. tăng {0}.</t>
+          <t>Crit. Rate tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Tỉ lệ Crit. tăng {0}.</t>
+          <t>Crit. Rate tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Tỉ lệ Crit. tăng {0}.</t>
+          <t>Crit. Rate tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus tăng thêm {0}.</t>
+          <t>Thêm Sát Thương Băng giá tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus+</t>
+          <t>Thêm Sát Thương Băng giá+</t>
         </is>
       </c>
     </row>
@@ -22999,7 +22999,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -23064,7 +23064,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -23194,7 +23194,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus tăng thêm {0}.</t>
+          <t>Thêm Sát Thương Băng giá tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus+</t>
+          <t>Thêm Sát Thương Băng giá+</t>
         </is>
       </c>
     </row>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus tăng thêm {0}.</t>
+          <t>Thêm Sát Thương Băng giá tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -23454,7 +23454,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus+</t>
+          <t>Thêm Sát Thương Băng giá+</t>
         </is>
       </c>
     </row>
@@ -23519,7 +23519,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus tăng thêm {0}.</t>
+          <t>Thêm Sát Thương Băng giá tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -23844,7 +23844,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus+</t>
+          <t>Thêm Sát Thương Băng giá+</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus tăng {0}.</t>
+          <t>Thêm Sát Thương Hợp Thể tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus+</t>
+          <t>Tăng Sát Thương Fusion+</t>
         </is>
       </c>
     </row>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -24169,7 +24169,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus tăng {0}.</t>
+          <t>Thêm Sát Thương Hợp Thể tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -24364,7 +24364,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus+</t>
+          <t>Tăng Sát Thương Fusion+</t>
         </is>
       </c>
     </row>
@@ -24429,7 +24429,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus tăng {0}.</t>
+          <t>Thêm Sát Thương Hợp Thể tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus+</t>
+          <t>Tăng Sát Thương Fusion+</t>
         </is>
       </c>
     </row>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -24689,7 +24689,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24754,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -24819,7 +24819,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus tăng {0}.</t>
+          <t>Thêm Sát Thương Hợp Thể tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -24884,7 +24884,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus+</t>
+          <t>Tăng Sát Thương Fusion+</t>
         </is>
       </c>
     </row>
@@ -24949,7 +24949,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus tăng {0}.</t>
+          <t>Thêm Sát Thương Hợp Thể tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus+</t>
+          <t>Tăng Sát Thương Fusion+</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -25209,7 +25209,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus tăng {0}.</t>
+          <t>Thêm Sát Thương Hợp Thể tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -25404,7 +25404,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus+</t>
+          <t>Tăng Sát Thương Fusion+</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25469,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus tăng {0}.</t>
+          <t>Thêm Sát Thương Hợp Thể tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus+</t>
+          <t>Tăng Sát Thương Fusion+</t>
         </is>
       </c>
     </row>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -25664,7 +25664,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -25859,7 +25859,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus tăng {0}.</t>
+          <t>Thêm Sát Thương Hợp Thể tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus+</t>
+          <t>Tăng Sát Thương Fusion+</t>
         </is>
       </c>
     </row>
@@ -25989,7 +25989,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus tăng {0}.</t>
+          <t>Thêm Sát Thương Hợp Thể tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus+</t>
+          <t>Tăng Sát Thương Fusion+</t>
         </is>
       </c>
     </row>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -26249,7 +26249,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus tăng {0}.</t>
+          <t>Thêm Sát Thương Hợp Thể tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus+</t>
+          <t>Tăng Sát Thương Fusion+</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus tăng {0}.</t>
+          <t>Thêm Sát Thương Hợp Thể tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -26574,7 +26574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus+</t>
+          <t>Tăng Sát Thương Fusion+</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -26704,7 +26704,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -26769,7 +26769,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus tăng {0}.</t>
+          <t>Thêm Sát Thương Hợp Thể tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus+</t>
+          <t>Tăng Sát Thương Fusion+</t>
         </is>
       </c>
     </row>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus tăng thêm {0}.</t>
+          <t>Thêm Sát Thương Băng giá tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -27094,7 +27094,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus+</t>
+          <t>Thêm Sát Thương Băng giá+</t>
         </is>
       </c>
     </row>
